--- a/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
@@ -14598,19 +14598,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -14630,19 +14630,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -14689,19 +14689,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="G5" t="n">
         <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4827586206896552</v>
       </c>
     </row>
     <row r="6">
@@ -14967,19 +14967,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="G14" t="n">
         <v>11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="15">
@@ -15090,19 +15090,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>0.85</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="G18" t="n">
         <v>33</v>
       </c>
       <c r="H18" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
     </row>
     <row r="19">
@@ -15117,19 +15117,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E19" t="n">
         <v>113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8968253968253969</v>
+        <v>0.8692307692307693</v>
       </c>
       <c r="G19" t="n">
         <v>94</v>
       </c>
       <c r="H19" t="n">
-        <v>0.746031746031746</v>
+        <v>0.7230769230769231</v>
       </c>
     </row>
   </sheetData>
@@ -15247,19 +15247,19 @@
         </is>
       </c>
       <c r="D4" s="20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>10</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>2</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -15271,19 +15271,19 @@
         </is>
       </c>
       <c r="D5" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="17" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>6</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -15319,19 +15319,19 @@
       </c>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>26</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>1</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>14</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4827586206896552</v>
       </c>
     </row>
     <row r="8">
@@ -15547,19 +15547,19 @@
         </is>
       </c>
       <c r="D16" s="20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>10</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="G16" s="17" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="17">
@@ -15643,19 +15643,19 @@
       </c>
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="24" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" s="23" t="n">
         <v>34</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.85</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>33</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
     </row>
     <row r="21">
@@ -15671,19 +15671,19 @@
       </c>
       <c r="C21" s="12" t="inlineStr"/>
       <c r="D21" s="24" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E21" s="23" t="n">
         <v>113</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>0.8968253968253969</v>
+        <v>0.8692307692307693</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>94</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>0.746031746031746</v>
+        <v>0.7230769230769231</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
@@ -926,32 +926,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688858234639755</t>
+          <t>1688855925819373</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -963,29 +963,24 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1030,32 +1025,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688854700793351</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1074,17 +1069,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1129,7 +1124,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688855990601283</t>
+          <t>1688857814474461</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1139,22 +1134,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1178,12 +1173,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1228,32 +1223,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857983840940</t>
+          <t>1688854717819330</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1272,17 +1267,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1317,7 +1312,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1327,7 +1322,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1337,22 +1332,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1367,7 +1362,12 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1376,17 +1376,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1426,32 +1426,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688857632794248</t>
+          <t>1688854346786888</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1463,24 +1463,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1525,32 +1530,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1569,17 +1574,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1624,7 +1629,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688856168895775</t>
+          <t>1688857382830184</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1639,22 +1644,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1673,12 +1678,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1723,7 +1728,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1738,17 +1743,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1772,12 +1777,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1812,7 +1817,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1822,7 +1827,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688857632794423</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1832,22 +1837,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1859,12 +1864,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854346786588</t>
+          <t>1688856520845931</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2025,71 +2025,61 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688856804923400</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2134,32 +2124,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688857587778504</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2178,17 +2168,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2233,32 +2223,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688857632794373</t>
+          <t>1688856520846151</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2277,17 +2267,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2332,7 +2322,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688857749872444</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2347,17 +2337,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2381,12 +2371,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2431,32 +2421,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688856504741446</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2475,17 +2465,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2530,7 +2520,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688856840766973,1688857529572218</t>
+          <t>1688856733864938</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2545,34 +2535,29 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -2584,12 +2569,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2634,32 +2619,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688854735807615</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2678,17 +2663,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2733,32 +2718,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857632794260</t>
+          <t>1688857104713888</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2773,26 +2758,21 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2837,32 +2817,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688857632794327</t>
+          <t>1688854745834995</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2871,42 +2851,27 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2951,32 +2916,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688855968871592,1688857401525365</t>
+          <t>1688857632794362</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2995,17 +2960,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3050,7 +3015,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3065,22 +3030,22 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -3099,12 +3064,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3139,7 +3104,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3149,32 +3114,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3186,29 +3151,39 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3248,32 +3223,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3285,24 +3260,29 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3347,32 +3327,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688855071729227</t>
+          <t>1688856733864930</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3384,24 +3364,29 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3436,7 +3421,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3446,7 +3431,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688854346786588</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3456,22 +3441,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3483,11 +3468,11 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>8,9,10,11,12,13</t>
+          <t>13,14,15</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -3500,17 +3485,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3540,7 +3525,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3550,37 +3535,37 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -3594,22 +3579,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3649,7 +3634,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688855034811328</t>
+          <t>1688857382830184</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3664,17 +3649,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3698,12 +3683,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3748,66 +3733,66 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688854346786888</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3842,7 +3827,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3852,37 +3837,37 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688858067856980</t>
+          <t>1688858076923296</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -3892,31 +3877,26 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -3956,32 +3936,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857885896779</t>
+          <t>1688857250838140</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3993,29 +3973,24 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>9,10,11,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4050,7 +4025,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4060,32 +4035,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4097,34 +4072,29 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4164,7 +4134,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688856840766973,1688857529572218</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4174,27 +4144,27 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -4213,12 +4183,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4263,37 +4233,37 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688858311666546</t>
+          <t>1688857749872459</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -4307,17 +4277,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4362,32 +4332,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688857104713888</t>
+          <t>1688856168895775</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4406,17 +4376,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4451,7 +4421,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4461,32 +4431,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688856531901583</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4505,22 +4475,22 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4560,32 +4530,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688855034811328</t>
+          <t>1688857529572218,1688856840766973</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4604,17 +4574,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4659,7 +4629,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688856504741386</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4669,22 +4639,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4696,7 +4666,12 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -4708,12 +4683,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4758,37 +4733,37 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688856187931317</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -4802,17 +4777,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4847,7 +4822,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4857,71 +4832,66 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M41" t="n">
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -4961,37 +4931,37 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688854745834995</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -5005,17 +4975,17 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5060,32 +5030,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688857471687073</t>
+          <t>1688856187931330</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5104,17 +5074,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5159,32 +5129,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688857950813447</t>
+          <t>1688856733864912</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5196,29 +5166,24 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5263,32 +5228,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857859856215</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5307,17 +5272,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5362,32 +5327,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688856520846151</t>
+          <t>1688857528801388</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5402,26 +5367,21 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>6,8,9,10,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5456,7 +5416,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5466,66 +5426,71 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688856187931330</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5565,32 +5530,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688856804923405</t>
+          <t>1688856504741386</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5609,17 +5574,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5654,7 +5619,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5664,32 +5629,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688856733864930</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5708,22 +5673,22 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -5763,37 +5728,37 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688857472723498</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -5807,17 +5772,17 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5862,32 +5827,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856504741335</t>
+          <t>1688856733864930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5899,24 +5864,29 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5961,37 +5931,37 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688858397734047</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -6005,17 +5975,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6060,7 +6030,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688858076923296</t>
+          <t>1688854902879055</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6075,17 +6045,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6109,12 +6079,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6149,7 +6119,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6159,37 +6129,37 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -6203,22 +6173,22 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -6258,37 +6228,37 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688857587778504</t>
+          <t>1688855034811328</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -6302,17 +6272,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6347,7 +6317,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6357,37 +6327,37 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854717819330</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -6401,22 +6371,22 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -6456,32 +6426,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688856504741288</t>
+          <t>1688857749872459</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6493,29 +6463,24 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6560,32 +6525,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857484684695</t>
+          <t>1688856706895732</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6597,24 +6562,29 @@
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6659,32 +6629,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688855593870536</t>
+          <t>1688858083589918</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6703,17 +6673,17 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6758,7 +6728,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688855319787208</t>
+          <t>1688857632794248</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6773,22 +6743,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -6807,12 +6777,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6857,32 +6827,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688857250838140</t>
+          <t>1688855071729227</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6901,17 +6871,17 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6956,7 +6926,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688856854514012,未上报</t>
+          <t>1688855034811328</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6966,22 +6936,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6990,28 +6960,13 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -7020,12 +6975,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7060,7 +7015,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7070,66 +7025,76 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688855925819373</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -7169,32 +7134,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688858188639828</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7213,17 +7178,17 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7258,7 +7223,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7268,48 +7233,48 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688856961861713</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M65" t="n">
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10</t>
         </is>
       </c>
       <c r="Q65" t="n">
@@ -7317,22 +7282,22 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -7372,7 +7337,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688858356858328</t>
+          <t>1688857749872444</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7387,17 +7352,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7421,12 +7386,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7486,7 +7451,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7575,32 +7540,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688857529572218,1688856840766973</t>
+          <t>1688857632794423</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7609,32 +7574,42 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O68" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>秦宇浩</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>qinyuhao</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7669,7 +7644,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7679,32 +7654,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688857258634877</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7723,22 +7698,22 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -7778,7 +7753,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688854957840124</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7793,17 +7768,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7818,12 +7793,7 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7832,12 +7802,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7882,7 +7852,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688857632794248</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7892,27 +7862,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -7931,12 +7901,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7981,37 +7951,37 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688857382830184</t>
+          <t>1688857471687073</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -8025,17 +7995,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8070,7 +8040,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8080,7 +8050,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688856168895797</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -8090,27 +8060,27 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -8129,17 +8099,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -8179,7 +8149,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688857257880743</t>
+          <t>1688856804923405</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -8189,22 +8159,22 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8228,12 +8198,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8278,32 +8248,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688854735807615</t>
+          <t>1688856854514012</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8318,26 +8288,26 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,21,22,23</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8382,7 +8352,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688857632794373</t>
+          <t>1688854957840114</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8392,27 +8362,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -8431,12 +8401,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8481,32 +8451,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688854745905297</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8518,24 +8488,29 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8580,32 +8555,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8624,17 +8599,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8679,32 +8654,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688857118654801</t>
+          <t>1688856504741446</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8723,17 +8698,17 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8778,32 +8753,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688855968871592,1688857401525365</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8822,17 +8797,17 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8877,66 +8852,61 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688856706895732</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M81" t="n">
         <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8981,37 +8951,37 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688857749872459</t>
+          <t>1688857632794373</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M82" t="n">
@@ -9025,17 +8995,17 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -9080,7 +9050,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688855319787208</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9090,27 +9060,27 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M83" t="n">
@@ -9129,12 +9099,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -9179,37 +9149,37 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688856531901583</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -9223,17 +9193,17 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -9268,7 +9238,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9278,7 +9248,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688856168895797</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9288,22 +9258,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9327,17 +9297,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -9377,32 +9347,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688857885896779</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9414,24 +9384,29 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,17</t>
+        </is>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9476,61 +9451,76 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688855319787208</t>
+          <t>1688856187931234</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -9575,32 +9565,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688854970874060</t>
+          <t>1688857484684695</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9619,17 +9609,17 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -9674,37 +9664,37 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688857382830184</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M89" t="n">
@@ -9718,17 +9708,17 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -9763,7 +9753,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9773,7 +9763,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688857632794248</t>
+          <t>1688858067856980</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9783,22 +9773,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9813,7 +9803,12 @@
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9822,17 +9817,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W90" t="inlineStr">
@@ -9872,7 +9867,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688858083589918</t>
+          <t>1688858356858328</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9882,22 +9877,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9921,12 +9916,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9971,37 +9966,37 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688857983840940</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -10015,17 +10010,17 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -10070,32 +10065,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688857749872459</t>
+          <t>1688855154879768</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10107,24 +10102,29 @@
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -10169,32 +10169,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688856187931267</t>
+          <t>1688857632794260</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -10268,37 +10268,37 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688854700793351</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -10312,17 +10312,17 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -10367,66 +10367,61 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688858234639755</t>
+          <t>1688856168895940</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M96" t="n">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -10471,37 +10466,37 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -10515,17 +10510,17 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -10570,76 +10565,61 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688858213891414</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>侯鑫冉</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>houxinran01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -10684,32 +10664,32 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688857472723498</t>
+          <t>1688857525693645</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10728,17 +10708,17 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -10773,7 +10753,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10783,32 +10763,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10827,22 +10807,22 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -10882,7 +10862,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688854745905297</t>
+          <t>1688855593870536</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10897,17 +10877,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10919,11 +10899,11 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -10936,12 +10916,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10986,7 +10966,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688856733864930</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10996,27 +10976,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -11035,12 +11015,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -11075,7 +11055,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11085,32 +11065,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688854847586533</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -11129,22 +11109,22 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -11174,7 +11154,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11184,7 +11164,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688854957840114</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -11194,22 +11174,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -11221,7 +11201,12 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -11233,17 +11218,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -11273,7 +11258,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11283,32 +11268,32 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688857257880743</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -11327,22 +11312,22 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -11382,37 +11367,37 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -11426,17 +11411,17 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -11471,7 +11456,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11481,37 +11466,37 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688857258634877</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -11525,22 +11510,22 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
@@ -11580,32 +11565,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11624,17 +11609,17 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -11669,7 +11654,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11679,32 +11664,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688856804923400</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11713,32 +11698,47 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q109" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -11778,32 +11778,32 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1688857632794362</t>
+          <t>1688857118654801</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -11976,32 +11976,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1688858397734047</t>
+          <t>1688854847586533</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -12020,17 +12020,17 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1688857814474461</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -12119,22 +12119,22 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1688856520845931</t>
+          <t>1688854957840124</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12184,22 +12184,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12214,7 +12214,12 @@
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -12223,12 +12228,12 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -12273,37 +12278,37 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1688855154879793</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -12317,17 +12322,17 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -12372,32 +12377,32 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688856504741288</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -12409,24 +12414,29 @@
         <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -12471,32 +12481,32 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1688855154879768</t>
+          <t>1688855990601283</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -12508,29 +12518,24 @@
         <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q117" t="n">
         <v>1</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -12565,7 +12570,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12575,32 +12580,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1688856187931317</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -12619,22 +12624,22 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -12674,7 +12679,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1688857525693645</t>
+          <t>1688856504741335</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -12684,22 +12689,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12711,12 +12716,7 @@
         <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q119" t="n">
         <v>1</v>
@@ -12728,12 +12728,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -12788,27 +12788,27 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -12827,17 +12827,17 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -12877,37 +12877,37 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688855154879793</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -12921,22 +12921,22 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -12976,37 +12976,37 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1688858188639828</t>
+          <t>1688857632794373</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -13020,17 +13020,17 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -13075,32 +13075,32 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1688858356858333</t>
+          <t>1688858311666546</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13112,29 +13112,24 @@
         <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q123" t="n">
         <v>1</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -13179,32 +13174,32 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1688856961861713</t>
+          <t>1688856187931267</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -13223,17 +13218,17 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -13278,32 +13273,32 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1688857528801388</t>
+          <t>1688857632794327</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -13312,27 +13307,42 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q125" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张晨阳</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangchenyang</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -13377,32 +13387,32 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1688856733864938</t>
+          <t>1688857859856215</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -13421,17 +13431,17 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -13476,37 +13486,37 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688855319787208</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -13520,17 +13530,17 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -13565,7 +13575,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -13575,37 +13585,37 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1688856168895940</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -13619,22 +13629,22 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -13674,32 +13684,32 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1688856733864912</t>
+          <t>1688857950813447</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -13718,17 +13728,17 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -13773,32 +13783,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1688854957840073</t>
+          <t>1688858356858333</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13817,17 +13827,17 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -13872,61 +13882,66 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688854970874060</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M131" t="n">
         <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -13971,7 +13986,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1688854902879055</t>
+          <t>1688854957840073</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -13981,22 +13996,22 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -14020,12 +14035,12 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -14117,19 +14132,19 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -14176,19 +14191,19 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" t="n">
         <v>16</v>
       </c>
-      <c r="E4" t="n">
-        <v>15</v>
-      </c>
       <c r="F4" t="n">
-        <v>0.9375</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>0.75</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="5">
@@ -14217,10 +14232,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="6">
@@ -14243,10 +14258,10 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
@@ -14302,16 +14317,16 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="9">
@@ -14604,19 +14619,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9595959595959596</v>
+        <v>0.97</v>
       </c>
       <c r="G18" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H18" t="n">
-        <v>0.898989898989899</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -14646,7 +14661,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄高短）-10月8日</t>
+          <t>企微风灵全天在线情况通晒（石家庄高短）-10月9日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -14734,19 +14749,19 @@
         </is>
       </c>
       <c r="D4" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>7</v>
-      </c>
       <c r="F4" s="21" t="n">
-        <v>0.875</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -14782,19 +14797,19 @@
       </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="23" t="n">
-        <v>15</v>
-      </c>
       <c r="F6" s="25" t="n">
-        <v>0.9375</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0.75</v>
+        <v>0.7647058823529411</v>
       </c>
     </row>
     <row r="7">
@@ -14819,10 +14834,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="8">
@@ -14837,10 +14852,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G8" s="17" t="n">
         <v>5</v>
@@ -14885,16 +14900,16 @@
         <v>26</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="11">
@@ -15134,19 +15149,19 @@
       </c>
       <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="24" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.9595959595959596</v>
+        <v>0.97</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.898989898989899</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X132"/>
+  <dimension ref="A1:X130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,32 +926,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688855925819373</t>
+          <t>1688855154879793</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -963,24 +963,29 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1025,37 +1030,37 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854700793351</t>
+          <t>1688856504741335</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -1069,17 +1074,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1124,7 +1129,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688857814474461</t>
+          <t>1688856504741446</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1134,22 +1139,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1173,12 +1178,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1223,37 +1228,37 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854717819330</t>
+          <t>1688855319787208</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1267,17 +1272,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1322,32 +1327,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688856733864938</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1359,29 +1364,29 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1416,7 +1421,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1426,32 +1431,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854346786888</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1463,34 +1468,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>刘亚雄</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>liuyaxiong</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1530,32 +1530,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688856804923400</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1570,21 +1570,26 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>万士兴</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>wanshixing</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1629,7 +1634,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688857382830184</t>
+          <t>1688854957840124</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1644,22 +1649,22 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1678,12 +1683,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>王云</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>wangyun</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1718,7 +1723,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1728,37 +1733,37 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688856531901583</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1772,22 +1777,22 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1827,32 +1832,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688857471687073</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1867,26 +1872,31 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1926,32 +1936,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688856520845931</t>
+          <t>1688857749872444</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1970,17 +1980,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>侯梅婷</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>houmeiting</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2025,32 +2035,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2062,24 +2072,29 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2114,7 +2129,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2124,32 +2139,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688857587778504</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2168,22 +2183,22 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2223,7 +2238,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688856520846151</t>
+          <t>1688856504741288</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2233,22 +2248,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2272,12 +2287,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2312,7 +2327,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2322,32 +2337,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2366,22 +2381,22 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2421,7 +2436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688857258634877</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2431,22 +2446,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2470,12 +2485,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2520,32 +2535,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688856733864938</t>
+          <t>1688856168895775</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2564,17 +2579,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>王思雨</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>wangsiyu07</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2619,32 +2634,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854735807615</t>
+          <t>1688857250838140</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2663,17 +2678,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2718,32 +2733,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857104713888</t>
+          <t>1688854847586533</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2755,24 +2770,29 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2817,32 +2837,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688854745834995</t>
+          <t>1688857525693645</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2861,17 +2881,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2916,37 +2936,37 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688857632794362</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -2960,17 +2980,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3005,7 +3025,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3015,32 +3035,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688854346786888</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3052,29 +3072,34 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>刘亚雄</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>liuyaxiong</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3104,7 +3129,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3114,32 +3139,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688855071729227</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3151,39 +3176,29 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3223,66 +3238,61 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688858234639755</t>
+          <t>1688856168895940</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3327,66 +3337,61 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688856733864930</t>
+          <t>1688857632794248</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>陈慧敏</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>chenhuimin01</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3421,7 +3426,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3431,7 +3436,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688854346786588</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3441,39 +3446,34 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -3485,17 +3485,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3535,32 +3535,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3634,32 +3634,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688857382830184</t>
+          <t>1688857885896779</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>寇紫璇</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>kouzixuan01</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688856168895797</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3748,37 +3748,37 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,16,17,18,19</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>赵鑫杨</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhaoxinyang</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688858076923296</t>
+          <t>1688856520846151</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3847,22 +3847,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3877,7 +3877,12 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>6,7,9,10,11</t>
+        </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3886,12 +3891,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3936,32 +3941,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857250838140</t>
+          <t>1688857587778504</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3980,17 +3985,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4035,7 +4040,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4050,22 +4055,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M33" t="n">
@@ -4084,12 +4089,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4134,32 +4139,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688856840766973,1688857529572218</t>
+          <t>1688857382830184</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4178,17 +4183,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4233,7 +4238,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688857749872459</t>
+          <t>1688856733864912</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4243,27 +4248,27 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -4282,12 +4287,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4322,7 +4327,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4332,7 +4337,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688856168895775</t>
+          <t>1688858067856980</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4342,37 +4347,52 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -4381,17 +4401,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>董常依娃</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>dongchangyiwa</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4421,7 +4441,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4431,32 +4451,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688856531901583</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4475,22 +4495,22 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -4530,37 +4550,37 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688857529572218,1688856840766973</t>
+          <t>1688855319787208</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -4574,17 +4594,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>王雪菲</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>wangxuefei</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4629,7 +4649,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688858234639755</t>
+          <t>1688858397734047</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4639,22 +4659,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4666,12 +4686,7 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
@@ -4683,12 +4698,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>陈嘉博</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>chenjiabo</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4733,37 +4748,37 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688856187931317</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -4777,17 +4792,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4832,32 +4847,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4869,24 +4884,29 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4946,7 +4966,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4971,7 +4991,12 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -5030,32 +5055,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688856187931330</t>
+          <t>1688855990601283</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -5074,17 +5099,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5129,7 +5154,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688856733864912</t>
+          <t>1688858083589918</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5139,22 +5164,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5178,12 +5203,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>王佳鹤</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>wangjiahe02</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5228,32 +5253,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688857814474461</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5272,17 +5297,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5327,7 +5352,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857528801388</t>
+          <t>1688856733864930</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5337,27 +5362,27 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -5376,12 +5401,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5416,7 +5441,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5426,71 +5451,66 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688855925819373</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M47" t="n">
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -5530,32 +5550,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688856504741386</t>
+          <t>1688855968871592,1688857401525365</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5574,17 +5594,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5619,7 +5639,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5629,37 +5649,37 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688858265888031</t>
+          <t>1688857950813447</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -5673,22 +5693,22 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>师佳佳</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>shijiajia</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
@@ -5728,32 +5748,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688857472723498</t>
+          <t>1688856733864930</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5772,17 +5792,17 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>张宝芮</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>zhangbaorui</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5827,66 +5847,61 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856733864930</t>
+          <t>1688854717819330</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M51" t="n">
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>王海旭</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>wanghaixu</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5931,32 +5946,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688858397734047</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5975,17 +5990,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6030,7 +6045,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688854902879055</t>
+          <t>1688854745905297</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6040,22 +6055,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -6067,7 +6082,12 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -6079,12 +6099,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6119,7 +6139,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6129,32 +6149,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6173,22 +6193,22 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -6228,7 +6248,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688855034811328</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6238,27 +6258,27 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -6277,12 +6297,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6317,7 +6337,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6327,37 +6347,37 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688857472723498</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -6371,22 +6391,22 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -6426,32 +6446,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688857749872459</t>
+          <t>1688857632794260</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6470,17 +6490,17 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>杨洋</t>
+          <t>檀小溪</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>yangyang04</t>
+          <t>tanxiaoxi</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6525,66 +6545,61 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688856706895732</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M58" t="n">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6629,32 +6644,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688858083589918</t>
+          <t>1688856187931330</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6673,17 +6688,17 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6743,7 +6758,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6758,7 +6773,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -6827,32 +6842,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688855071729227</t>
+          <t>1688857632794373</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6871,17 +6886,17 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6926,32 +6941,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688855034811328</t>
+          <t>1688857528801388</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6970,17 +6985,17 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张慧</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhanghui03</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7025,7 +7040,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688857545861192</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -7040,17 +7055,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7062,20 +7077,10 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -7084,12 +7089,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>冉语嫣</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>ranyuyan</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7134,37 +7139,37 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688858188639828</t>
+          <t>1688857632794373</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M64" t="n">
@@ -7178,17 +7183,17 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>贾云飞</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>jiayunfei</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7233,7 +7238,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688856961861713</t>
+          <t>1688854902879055</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7243,22 +7248,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7270,12 +7275,7 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7337,37 +7337,37 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688857749872444</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -7377,26 +7377,31 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -7436,66 +7441,61 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688856733864924</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M67" t="n">
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688857632794423</t>
+          <t>1688857118654801</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7550,22 +7550,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7574,28 +7574,13 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -7604,12 +7589,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>秦宇浩</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>qinyuhao</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7654,37 +7639,37 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688857983840940</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -7698,17 +7683,17 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7753,7 +7738,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7763,22 +7748,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7802,12 +7787,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7852,32 +7837,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688857632794248</t>
+          <t>1688858311666546</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7896,17 +7881,17 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>陈慧敏</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>chenhuimin01</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7951,32 +7936,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688857471687073</t>
+          <t>1688854957840114</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7995,17 +7980,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>郭宁</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>guoning02</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8040,7 +8025,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8050,37 +8035,37 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688858076923296</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -8094,22 +8079,22 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -8139,7 +8124,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -8149,32 +8134,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688856804923405</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8193,22 +8178,22 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -8248,37 +8233,37 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688856854514012</t>
+          <t>1688857749872459</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -8288,26 +8273,21 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.05555555555555555</v>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8352,61 +8332,66 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688854957840114</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M76" t="n">
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>郭宁</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>guoning02</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8451,32 +8436,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688854745905297</t>
+          <t>1688858356858333</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8488,29 +8473,24 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8555,32 +8535,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8599,17 +8579,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8654,32 +8634,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688856504741446</t>
+          <t>1688857749872459</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8698,17 +8678,17 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>杨洋</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>yangyang04</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8753,7 +8733,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688855968871592,1688857401525365</t>
+          <t>1688858188639828</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8763,22 +8743,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8787,13 +8767,28 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8802,12 +8797,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>王泽壮</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>wangzezhuang</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8852,37 +8847,37 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688854700793351</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -8896,17 +8891,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8951,7 +8946,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688857632794373</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8961,22 +8956,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -9000,12 +8995,12 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -9050,7 +9045,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688855319787208</t>
+          <t>1688856504741386</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9065,17 +9060,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9099,12 +9094,12 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -9149,37 +9144,37 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688857104713888</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -9193,17 +9188,17 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -9238,7 +9233,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -9248,7 +9243,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688856168895797</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9258,22 +9253,22 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9288,7 +9283,12 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -9297,17 +9297,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>赵鑫杨</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>zhaoxinyang</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -9347,32 +9347,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688857885896779</t>
+          <t>1688854346786588</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9384,29 +9384,24 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>张天笑</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhangtianxiao</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9451,32 +9446,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688856187931234</t>
+          <t>1688857484684695</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9485,42 +9480,27 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -9565,7 +9545,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688857484684695</t>
+          <t>1688856854514012</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9580,17 +9560,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9605,7 +9585,12 @@
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -9614,12 +9599,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -9664,61 +9649,66 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688856733864924</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M89" t="n">
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q89" t="n">
         <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -9763,7 +9753,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688858067856980</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9778,22 +9768,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M90" t="n">
@@ -9803,12 +9793,7 @@
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -9817,12 +9802,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9867,32 +9852,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688858356858328</t>
+          <t>1688855154879768</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9904,24 +9889,29 @@
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>王佳佳</t>
+          <t>张军妹</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>wangjiajia02</t>
+          <t>zhangjunmei</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9966,37 +9956,37 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688857983840940</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M92" t="n">
@@ -10010,17 +10000,17 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -10055,7 +10045,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10065,7 +10055,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688855154879768</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -10075,39 +10065,34 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M93" t="n">
         <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
         <v>1</v>
@@ -10119,17 +10104,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>张军妹</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>zhangjunmei</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -10169,32 +10154,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688857632794260</t>
+          <t>1688854957840073</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10213,17 +10198,17 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>檀小溪</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>tanxiaoxi</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -10268,61 +10253,66 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688856706895732</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M95" t="n">
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q95" t="n">
         <v>1</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -10357,7 +10347,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10367,66 +10357,71 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688856168895940</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M96" t="n">
         <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
@@ -10466,32 +10461,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688856504741335</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10510,17 +10505,17 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -10565,7 +10560,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688857529572218,1688856840766973</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10580,22 +10575,22 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -10614,12 +10609,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -10664,7 +10659,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688857525693645</t>
+          <t>1688856520845931</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10674,22 +10669,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10698,13 +10693,28 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>18,19</t>
+        </is>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>18,19</t>
+        </is>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>18,19</t>
+        </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -10713,12 +10723,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>侯梅婷</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>houmeiting</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -10753,7 +10763,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10763,37 +10773,37 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -10807,22 +10817,22 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -10862,66 +10872,61 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688855593870536</t>
+          <t>1688855034811328</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M101" t="n">
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10966,61 +10971,66 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688856187931234</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M102" t="n">
         <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -11055,7 +11065,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11065,32 +11075,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688856961861713</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -11109,22 +11119,22 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -11154,7 +11164,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11164,32 +11174,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688856602829916</t>
+          <t>1688856804923405</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -11201,34 +11211,29 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>张雅楠</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>zhangyanan</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
@@ -11268,37 +11273,37 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688857257880743</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -11312,17 +11317,17 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -11367,32 +11372,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -11411,17 +11416,17 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -11466,32 +11471,32 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688857632794362</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11503,24 +11508,29 @@
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q107" t="n">
         <v>1</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -11565,37 +11575,37 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -11609,17 +11619,17 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -11664,32 +11674,32 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1688856804923400</t>
+          <t>1688858356858328</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -11698,42 +11708,27 @@
         </is>
       </c>
       <c r="M109" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -11778,32 +11773,32 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1688857118654801</t>
+          <t>1688856187931267</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -11822,17 +11817,17 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -11877,7 +11872,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1688856504741335</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -11887,27 +11882,27 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -11917,7 +11912,12 @@
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -11926,12 +11926,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -11976,32 +11976,32 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1688854847586533</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -12020,17 +12020,17 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -12174,32 +12174,32 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1688854957840124</t>
+          <t>1688854735807615</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -12214,26 +12214,21 @@
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>王云</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>wangyun</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -12278,32 +12273,32 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -12322,17 +12317,17 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -12377,7 +12372,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1688856504741288</t>
+          <t>1688855593870536</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -12392,17 +12387,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -12414,11 +12409,11 @@
         <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -12431,12 +12426,12 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -12481,37 +12476,37 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1688855990601283</t>
+          <t>1688857382830184</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -12525,17 +12520,17 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>寇紫璇</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>kouzixuan01</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -12570,7 +12565,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -12580,32 +12575,32 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1688857545861192</t>
+          <t>1688856187931317</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -12624,22 +12619,22 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>冉语嫣</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>ranyuyan</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -12679,32 +12674,32 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1688856504741335</t>
+          <t>1688857529572218,1688856840766973</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -12723,17 +12718,17 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -12778,32 +12773,32 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688857257880743</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -12822,17 +12817,17 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -12877,32 +12872,32 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1688855154879793</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -12914,24 +12909,29 @@
         <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q121" t="n">
         <v>1</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -12976,32 +12976,32 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1688857632794373</t>
+          <t>1688857258634877</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -13020,17 +13020,17 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>贾云飞</t>
+          <t>张晓芊</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>jiayunfei</t>
+          <t>zhangxiaoqian01</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -13075,32 +13075,32 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1688858311666546</t>
+          <t>1688854745834995</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-刘亚雄</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13119,17 +13119,17 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -13174,37 +13174,37 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1688856187931267</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -13218,17 +13218,17 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -13273,32 +13273,32 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1688857632794327</t>
+          <t>1688856602829916</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -13307,12 +13307,7 @@
         </is>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -13323,31 +13318,26 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>张晨阳</t>
+          <t>张雅楠</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>zhangchenyang</t>
+          <t>zhangyanan</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -13402,7 +13392,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13486,7 +13476,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1688855319787208</t>
+          <t>1688855034811328</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -13501,22 +13491,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -13535,12 +13525,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>王雪菲</t>
+          <t>张慧</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>wangxuefei</t>
+          <t>zhanghui03</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -13585,7 +13575,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688858265888031</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -13600,17 +13590,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -13634,12 +13624,12 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>师佳佳</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>shijiajia</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -13684,32 +13674,32 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1688857950813447</t>
+          <t>1688854970874060</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -13721,24 +13711,29 @@
         <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="Q129" t="n">
         <v>1</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -13783,32 +13778,32 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1688858356858333</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13827,17 +13822,17 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -13851,209 +13846,6 @@
         </is>
       </c>
       <c r="X130" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>20261009</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>高阶</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>高阶</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>1688854970874060</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>高阶一</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>云销雨霁-姚明</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>赵熙呈</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>zhaoxicheng</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M131" t="n">
-        <v>1</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Q131" t="n">
-        <v>1</v>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>高一</t>
-        </is>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>赵熙呈</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>zhaoxicheng</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>20261009</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>高阶</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>高阶</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1688854957840073</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>高阶一</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>如日方升</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>高明月</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>gaomingyue01</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M132" t="n">
-        <v>1</v>
-      </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>高一</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>高明月</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>gaomingyue01</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -14135,16 +13927,16 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -14173,10 +13965,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -14194,16 +13986,16 @@
         <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9411764705882353</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="5">
@@ -14226,16 +14018,16 @@
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="6">
@@ -14255,19 +14047,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -14290,10 +14082,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G7" t="n">
         <v>8</v>
@@ -14314,19 +14106,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.84</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="9">
@@ -14501,16 +14293,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -14592,19 +14384,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9722222222222222</v>
       </c>
     </row>
     <row r="18">
@@ -14619,19 +14411,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F18" t="n">
-        <v>0.97</v>
+        <v>0.9591836734693877</v>
       </c>
       <c r="G18" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" t="n">
-        <v>0.87</v>
+        <v>0.8775510204081632</v>
       </c>
     </row>
   </sheetData>
@@ -14661,7 +14453,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄高短）-10月9日</t>
+          <t>企微风灵全天在线情况通晒（石家庄高短）-10月11日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -14752,16 +14544,16 @@
         <v>9</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="5">
@@ -14782,10 +14574,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>0.875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="6">
@@ -14800,16 +14592,16 @@
         <v>17</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>0.9411764705882353</v>
+        <v>1</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="7">
@@ -14828,16 +14620,16 @@
         <v>11</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="8">
@@ -14849,19 +14641,19 @@
         </is>
       </c>
       <c r="D8" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G8" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="21" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>5</v>
-      </c>
       <c r="H8" s="21" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -14876,10 +14668,10 @@
         <v>8</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>8</v>
@@ -14897,19 +14689,19 @@
       </c>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.84</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="11">
@@ -15049,16 +14841,16 @@
         </is>
       </c>
       <c r="D16" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>1</v>
@@ -15121,19 +14913,19 @@
       </c>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>0.972972972972973</v>
+        <v>0.9722222222222222</v>
       </c>
     </row>
     <row r="20">
@@ -15149,19 +14941,19 @@
       </c>
       <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="24" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.97</v>
+        <v>0.9591836734693877</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.87</v>
+        <v>0.8775510204081632</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄高短/石家庄-石家庄高短-销售风灵在线率明细数据.xlsx
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X107"/>
+  <dimension ref="A1:X113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,32 +926,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688856531901583</t>
+          <t>1688856722866484</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -960,42 +960,27 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>卢晓萍</t>
+          <t>杨紫涵</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>luxiaoping</t>
+          <t>yangzihan02</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1040,32 +1025,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688857529572218,1688856840766973</t>
+          <t>1688856504741288</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1077,24 +1062,29 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>贾思薇</t>
+          <t>何安琪</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>jiasiwei</t>
+          <t>heanqi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1139,37 +1129,37 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688856804923400</t>
+          <t>1688857749872444</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -1179,26 +1169,21 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>万士兴</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>wanshixing</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1243,71 +1228,61 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854777850591</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>杨洪懿</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>yanghongyi01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>杨洪懿</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>yanghongyi01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1352,37 +1327,37 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -1396,17 +1371,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1451,37 +1426,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688858213891390</t>
+          <t>1688856168895940</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M7" t="n">
@@ -1495,17 +1470,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>刘亚妮</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>liuyani01</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1550,66 +1525,61 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688854745905297</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>白超洋</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>baichaoyang01</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1654,32 +1624,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688855071729227</t>
+          <t>1688858397734047</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1698,17 +1668,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>路跃威</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>luyuewei</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1753,37 +1723,37 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688856504741386</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -1797,17 +1767,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1852,32 +1822,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688856504741335</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1892,26 +1862,21 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>任紫菡</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>renzihan</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1956,32 +1921,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688857104713888</t>
+          <t>1688857786701503</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>baitie</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1996,21 +1961,26 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>仲文璇</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zhongwenxuan01</t>
+          <t>baitie</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2045,7 +2015,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2055,32 +2025,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854397788387</t>
+          <t>1688854847586533</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2095,31 +2065,26 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>王义明</t>
+          <t>李肖雨</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>wangyiming</t>
+          <t>lixiaoyu</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2159,7 +2124,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688858356858333</t>
+          <t>1688856722866488</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2174,17 +2139,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2196,12 +2161,7 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -2213,12 +2173,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>张倍溪</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>zhangbeixi01</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2263,32 +2223,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688856187931267</t>
+          <t>1688856520846151</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2303,26 +2263,21 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>周士杰</t>
+          <t>吴国强</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>zhoushijie01</t>
+          <t>wuguoqiang</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2367,32 +2322,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688857375861365</t>
+          <t>1688858356858328</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>田萌阳</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>tianmengyang</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2404,34 +2359,24 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>6,7,8,9</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>田萌阳</t>
+          <t>王佳佳</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>tianmengyang</t>
+          <t>wangjiajia02</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2466,7 +2411,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2476,32 +2421,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688858067856857</t>
+          <t>1688855990601283</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2513,34 +2458,34 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>10,11,12,13</t>
+        </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>周庆有</t>
+          <t>杨晨朝</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>zhouqingyou</t>
+          <t>yangchenchao01</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2570,7 +2515,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2580,32 +2525,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688858083589918</t>
+          <t>1688858173853397</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2624,22 +2569,22 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>祁婧婷</t>
+          <t>张文博</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>qijingting01</t>
+          <t>zhangwenbo01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2679,7 +2624,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688856520846151</t>
+          <t>1688854970874060</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2689,22 +2634,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2719,12 +2664,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>6,7,9,10,11,14,15,16,18,19,20,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2733,12 +2673,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>吴国强</t>
+          <t>赵熙呈</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>wuguoqiang</t>
+          <t>zhaoxicheng</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2783,61 +2723,66 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688856706895732</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M20" t="n">
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>梁杰</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>liangjie01</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2882,37 +2827,37 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688857749872444</t>
+          <t>1688857587778504</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -2926,17 +2871,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>郑小萌</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>zhengxiaomeng</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2981,32 +2926,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688855946578976</t>
+          <t>1688857814474461</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3025,17 +2970,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>贾桂敏</t>
+          <t>田亚茹</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>jiaguimin</t>
+          <t>tianyaru</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3080,32 +3025,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857749872444</t>
+          <t>1688858213891390</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3124,17 +3069,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>王泳淇</t>
+          <t>刘亚妮</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>wangyongqi01</t>
+          <t>liuyani01</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3169,7 +3114,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3179,32 +3124,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688854397789505</t>
+          <t>1688856804923405</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3223,22 +3168,22 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>商紫强</t>
+          <t>侯超飞</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>shangziqiang</t>
+          <t>houchaofei</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3278,32 +3223,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688856733864924</t>
+          <t>1688856961861713</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3315,11 +3260,11 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3327,17 +3272,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>张淏婷</t>
+          <t>张轩瑜</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>zhanghaoting</t>
+          <t>zhangxuanyu</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3382,32 +3327,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688857014907414</t>
+          <t>1688854717819330</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3426,17 +3371,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>焦泽晖</t>
+          <t>高紫佳</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>jiaozehui01</t>
+          <t>gaozijia</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3481,37 +3426,37 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688857250838140</t>
+          <t>1688854957840073</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -3525,17 +3470,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>高明月</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>gaomingyue01</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3570,7 +3515,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3580,32 +3525,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688855990601283</t>
+          <t>1688854397788387</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3624,22 +3569,22 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>杨晨朝</t>
+          <t>王义明</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>yangchenchao01</t>
+          <t>wangyiming</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -3679,37 +3624,37 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688854957840073</t>
+          <t>1688856168895775</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -3723,17 +3668,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>高明月</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>gaomingyue01</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3778,7 +3723,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688856168895940</t>
+          <t>1688857528801388</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3788,22 +3733,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3827,12 +3772,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>郭昱</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>guoyu</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3877,32 +3822,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688858356858343</t>
+          <t>1688856145888031</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3921,17 +3866,17 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>黄梦雅</t>
+          <t>朱浩楠</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>huangmengya</t>
+          <t>zhuhaonan</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3976,32 +3921,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688856531901583</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -4013,24 +3958,34 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>卢晓萍</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>luxiaoping</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4075,32 +4030,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688856504741446</t>
+          <t>1688857472723498</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4119,17 +4074,17 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>胡博宇</t>
+          <t>张宝芮</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>huboyu</t>
+          <t>zhangbaorui</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4174,7 +4129,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688854970874060</t>
+          <t>1688857471687073</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4184,22 +4139,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4223,12 +4178,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>赵熙呈</t>
+          <t>刘翔宇</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>zhaoxicheng</t>
+          <t>liuxiangyu</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4273,32 +4228,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688854745834995</t>
+          <t>1688856168895775</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4317,17 +4272,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>刘嘉蓓</t>
+          <t>赵佳鑫</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>liujiabei</t>
+          <t>zhaojiaxin01</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4362,7 +4317,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4372,32 +4327,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688855618814007</t>
+          <t>1688857041843101</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4416,22 +4371,22 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>董维强</t>
+          <t>邸思雨</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>dongweiqiang</t>
+          <t>disiyu</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4471,7 +4426,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688857250838140</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4486,22 +4441,22 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -4520,12 +4475,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>张立</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>zhangli02</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4570,32 +4525,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688858249747099</t>
+          <t>1688856187931317</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4607,29 +4562,24 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>卯亮亮</t>
+          <t>刘博文</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>maoliangliang02</t>
+          <t>liubowen02</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4674,32 +4624,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688855925819373</t>
+          <t>1688856854514012</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4708,27 +4658,42 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>李伟业</t>
+          <t>冯常增</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>liweiye02</t>
+          <t>fengchangzeng</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4773,32 +4738,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688856187931234</t>
+          <t>1688858249747099</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4810,11 +4775,11 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -4822,17 +4787,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>陈欢欢</t>
+          <t>卯亮亮</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>chenhuanhuan01</t>
+          <t>maoliangliang02</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4877,7 +4842,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688854717819330</t>
+          <t>1688854941520680</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4887,22 +4852,22 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4911,18 +4876,28 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O41" t="n">
-        <v>0.05555555555555555</v>
+        <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4931,12 +4906,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>高紫佳</t>
+          <t>刘帅</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>gaozijia</t>
+          <t>liushuai05</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4981,66 +4956,61 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688856168895940</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M42" t="n">
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>王朝威</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>wangzhaowei</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5085,7 +5055,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688854346786588</t>
+          <t>1688858397734047</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5095,39 +5065,34 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M43" t="n">
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>1</v>
@@ -5139,12 +5104,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张天笑</t>
+          <t>李如玮</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangtianxiao</t>
+          <t>liruwei</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5189,32 +5154,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688857632794362</t>
+          <t>1688855593870536</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5226,29 +5191,24 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>夏晓行</t>
+          <t>闫学辉</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>xiaxiaoxing</t>
+          <t>yanxuehui01</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5293,32 +5253,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857258634865</t>
+          <t>1688854717819422</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>姜志强</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>jiangzhiqiang</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5337,17 +5297,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>姜志强</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>jiangzhiqiang</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5392,7 +5352,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688858173853397</t>
+          <t>1688858067856857</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5407,17 +5367,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5432,11 +5392,11 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,23</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5446,12 +5406,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>张文博</t>
+          <t>周庆有</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>zhangwenbo01</t>
+          <t>zhouqingyou</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5496,32 +5456,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688854902879055</t>
+          <t>1688857484684695</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5540,17 +5500,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>楚胜杰</t>
+          <t>解博帆</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>chushengjie</t>
+          <t>xiebofan</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5585,7 +5545,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5595,32 +5555,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688857545861170</t>
+          <t>1688855154879793</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5639,22 +5599,22 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>刘洋</t>
+          <t>秦会乐</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>liuyang06</t>
+          <t>qinhuile01</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -5694,37 +5654,37 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688855713584928</t>
+          <t>1688858356858333</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M49" t="n">
@@ -5738,17 +5698,17 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>姚明</t>
+          <t>叶旭佳</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>yaoming01</t>
+          <t>yexujia</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5793,48 +5753,48 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688858356858333</t>
+          <t>1688856504741335</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>11,12,13</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -5842,17 +5802,17 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>叶旭佳</t>
+          <t>任紫菡</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>yexujia</t>
+          <t>renzihan</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5897,37 +5857,37 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856504741288</t>
+          <t>1688857525693645</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -5937,21 +5897,26 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>何安琪</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>heanqi</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5996,7 +5961,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688856706895732</t>
+          <t>1688856187931234</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -6006,22 +5971,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -6050,12 +6015,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>梁杰</t>
+          <t>陈欢欢</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>liangjie01</t>
+          <t>chenhuanhuan01</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6100,37 +6065,37 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688856504741311</t>
+          <t>1688857859856215</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -6144,17 +6109,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>张超</t>
+          <t>邢爱斌</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>zhangchao01</t>
+          <t>xingaibin01</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6199,37 +6164,37 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688856168895775</t>
+          <t>1688858311666546</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -6243,17 +6208,17 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>王嘉磊</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>wangjialei</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6298,32 +6263,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688857257880743</t>
+          <t>1688856733864938</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6335,24 +6300,29 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>张旗号</t>
+          <t>王思雨</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>zhangqihao01</t>
+          <t>wangsiyu07</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6397,61 +6367,66 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688854745905297</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M56" t="n">
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>白超洋</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>baichaoyang01</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6486,7 +6461,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6496,7 +6471,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688858397734047</t>
+          <t>1688857545861170</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6506,27 +6481,27 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M57" t="n">
@@ -6536,7 +6511,12 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -6545,17 +6525,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>刘洋</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>liuyang06</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -6595,32 +6575,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857814474461</t>
+          <t>1688858234639755</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6629,42 +6609,42 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13</t>
+          <t>9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.5</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22</t>
+          <t>9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>田亚茹</t>
+          <t>陈嘉博</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>tianyaru</t>
+          <t>chenjiabo</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6709,61 +6689,66 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688856168895940</t>
+          <t>1688857375861365</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>田萌阳</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>tianmengyang</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M59" t="n">
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>王朝威</t>
+          <t>田萌阳</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>wangzhaowei</t>
+          <t>tianmengyang</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6798,7 +6783,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6808,7 +6793,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688857041843101</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6818,39 +6803,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -6862,17 +6842,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>邸思雨</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>disiyu</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -6902,7 +6882,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6912,32 +6892,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688854735807615</t>
+          <t>1688854397789505</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6956,22 +6936,22 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>杨梦娇</t>
+          <t>商紫强</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>yangmengjiao</t>
+          <t>shangziqiang</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7011,32 +6991,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688857632794362</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -7055,17 +7035,17 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>夏晓行</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>xiaxiaoxing</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -7110,32 +7090,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688856722866484</t>
+          <t>1688854735807615</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>决胜千里-张韶开</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -7154,17 +7134,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>杨紫涵</t>
+          <t>杨梦娇</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>yangzihan02</t>
+          <t>yangmengjiao</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -7209,7 +7189,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688857632794389</t>
+          <t>1688857983840940</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7224,17 +7204,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>陈庆娴</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>chenqingxian</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7258,12 +7238,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>陈庆娴</t>
+          <t>刘云冰</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>chenqingxian</t>
+          <t>liuyunbing</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7308,32 +7288,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688856187931317</t>
+          <t>1688858083589918</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7352,17 +7332,17 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>刘博文</t>
+          <t>祁婧婷</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>liubowen02</t>
+          <t>qijingting01</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7407,7 +7387,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688857118654801</t>
+          <t>1688856955546120</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7417,22 +7397,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7456,12 +7436,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>张星玄</t>
+          <t>刘劲松</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>zhangxingxuan</t>
+          <t>liujinsong</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7506,32 +7486,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688855154879793</t>
+          <t>1688855946578976</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7543,29 +7523,24 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>秦会乐</t>
+          <t>贾桂敏</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>qinhuile01</t>
+          <t>jiaguimin</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7610,7 +7585,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688857794712832</t>
+          <t>1688854700793351</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7625,17 +7600,17 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7647,12 +7622,7 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
@@ -7664,12 +7634,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>王东发</t>
+          <t>黄思旭</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>wangdongfa</t>
+          <t>huangsixu</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7714,7 +7684,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688855593870536</t>
+          <t>1688857632794389</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -7724,22 +7694,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>陈庆娴</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>chenqingxian</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7763,12 +7733,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>闫学辉</t>
+          <t>陈庆娴</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>yanxuehui01</t>
+          <t>chenqingxian</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7813,7 +7783,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688856145888031</t>
+          <t>1688857885896779</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7828,17 +7798,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7847,28 +7817,13 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7877,12 +7832,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>朱浩楠</t>
+          <t>穆朝鹏</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>zhuhaonan</t>
+          <t>muchaopeng</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7927,32 +7882,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688854717819422</t>
+          <t>1688857794712832</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7961,27 +7916,42 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>17,18</t>
+        </is>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,17,18,22,23</t>
+        </is>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>17,18</t>
+        </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>王东发</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>wangdongfa</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -8026,32 +7996,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688856955546120</t>
+          <t>1688857257880743</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -8063,29 +8033,24 @@
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>刘劲松</t>
+          <t>张旗号</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>liujinsong</t>
+          <t>zhangqihao01</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -8120,7 +8085,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>高阶</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -8130,32 +8095,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688857786701503</t>
+          <t>1688854513957323</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>紫翼飞腾-商紫强</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>张雅超</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>baitie</t>
+          <t>zhangyachao</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -8167,34 +8132,29 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>张雅超</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>baitie</t>
+          <t>zhangyachao</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>高中</t>
+          <t>爱学</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -8234,32 +8194,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688857525693645</t>
+          <t>1688857258634865</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>姜志强</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>jiangzhiqiang</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8274,21 +8234,26 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>姜志强</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>jiangzhiqiang</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8333,32 +8298,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688858076923296</t>
+          <t>1688856504741311</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8370,29 +8335,24 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>刘松松</t>
+          <t>张超</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>liusongsong</t>
+          <t>zhangchao01</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8427,7 +8387,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -8437,7 +8397,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688854513957323</t>
+          <t>1688854717819422</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8447,27 +8407,27 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>张雅超</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zhangyachao</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -8486,17 +8446,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>张雅超</t>
+          <t>刘旭琳</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>zhangyachao</t>
+          <t>liuxulin</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -8536,32 +8496,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688854941520680</t>
+          <t>1688856504741421</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8570,42 +8530,27 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>刘帅</t>
+          <t>刘若凌</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>liushuai05</t>
+          <t>liuruoling</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8650,32 +8595,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688856504741421</t>
+          <t>1688855968871592,1688857401525365</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8694,17 +8639,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>刘若凌</t>
+          <t>张宇</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>liuruoling</t>
+          <t>zhangyu02</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8749,7 +8694,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688857950813447</t>
+          <t>1688856733864924</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8759,22 +8704,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8786,7 +8731,12 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
@@ -8798,12 +8748,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>刘晓畅</t>
+          <t>张淏婷</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>liuxiaochang</t>
+          <t>zhanghaoting</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8848,7 +8798,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688857885896779</t>
+          <t>1688857104713888</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8858,22 +8808,22 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8882,28 +8832,13 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -8912,12 +8847,12 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>穆朝鹏</t>
+          <t>仲文璇</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>muchaopeng</t>
+          <t>zhongwenxuan01</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8962,32 +8897,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688858188639828</t>
+          <t>1688854745834995</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -9006,17 +8941,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>王泽壮</t>
+          <t>刘嘉蓓</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>wangzezhuang</t>
+          <t>liujiabei</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -9061,32 +8996,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688857471687073</t>
+          <t>1688857749872491</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -9105,17 +9040,17 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>刘翔宇</t>
+          <t>王如梦</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>liuxiangyu</t>
+          <t>wangrumeng</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -9160,32 +9095,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688858397734047</t>
+          <t>1688856733864930</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -9194,27 +9129,42 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>李如玮</t>
+          <t>王海旭</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>liruwei</t>
+          <t>wanghaixu</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -9259,32 +9209,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688857258634877</t>
+          <t>1688858076923296</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -9303,17 +9253,17 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>张晓芊</t>
+          <t>刘松松</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>zhangxiaoqian01</t>
+          <t>liusongsong</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -9358,32 +9308,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688857528801388</t>
+          <t>1688857118654801</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>高阶三</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>经略四方-何佳泽</t>
+          <t>破浪前行-陈嘉博</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9402,17 +9352,17 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>高三</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>郭昱</t>
+          <t>张星玄</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>guoyu</t>
+          <t>zhangxingxuan</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -9457,7 +9407,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688854717819422</t>
+          <t>1688857250838140</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9467,22 +9417,22 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9506,12 +9456,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>刘旭琳</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>liuxulin</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9556,32 +9506,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688856804923405</t>
+          <t>1688857525693645</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶二</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9596,21 +9546,26 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高二</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>侯超飞</t>
+          <t>何玉涵</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>houchaofei</t>
+          <t>heyuhan</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -9655,32 +9610,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688856187931330</t>
+          <t>1688854902879055</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>继往开来-姜志强</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9699,17 +9654,17 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>孙建通</t>
+          <t>楚胜杰</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>sunjiantong01</t>
+          <t>chushengjie</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -9754,32 +9709,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688857983840940</t>
+          <t>1688856840766973</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>如日方升</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9798,17 +9753,17 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>刘云冰</t>
+          <t>贾思薇</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>liuyunbing</t>
+          <t>jiasiwei</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -9853,7 +9808,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688855073726560</t>
+          <t>1688856733864912</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9868,17 +9823,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9890,7 +9845,12 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>8,9,10</t>
+        </is>
       </c>
       <c r="Q90" t="n">
         <v>1</v>
@@ -9902,12 +9862,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>王泽</t>
+          <t>王佳鹤</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>wangze02</t>
+          <t>wangjiahe02</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9952,7 +9912,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688857587778504</t>
+          <t>1688857950813447</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9962,22 +9922,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9989,12 +9949,7 @@
         <v>1</v>
       </c>
       <c r="O91" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>14,15,16</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
@@ -10006,12 +9961,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>郑小萌</t>
+          <t>刘晓畅</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>zhengxiaomeng</t>
+          <t>liuxiaochang</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -10056,32 +10011,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688856504741386</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -10100,17 +10055,17 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -10145,7 +10100,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高阶</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -10155,32 +10110,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688858067856980</t>
+          <t>1688857528801400</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>紫翼飞腾-商紫强</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>王宇飞</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wangyufei01</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10189,32 +10144,47 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>董常依娃</t>
+          <t>王宇飞</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>dongchangyiwa</t>
+          <t>wangyufei01</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>爱学</t>
+          <t>高中</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -10254,7 +10224,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688857401525365,1688855968871592</t>
+          <t>1688856504741446</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -10264,22 +10234,22 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>云销雨霁-姚明</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10303,12 +10273,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>张宇</t>
+          <t>胡博宇</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>zhangyu02</t>
+          <t>huboyu</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -10353,7 +10323,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688856961861713</t>
+          <t>1688855713584928</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -10368,17 +10338,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10402,12 +10372,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>张轩瑜</t>
+          <t>姚明</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>zhangxuanyu</t>
+          <t>yaoming01</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -10452,7 +10422,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688856722866488</t>
+          <t>1688855618814007</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10462,27 +10432,27 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>骁腾问鼎-王立进</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -10501,12 +10471,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>张倍溪</t>
+          <t>董维强</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>zhangbeixi01</t>
+          <t>dongweiqiang</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -10551,32 +10521,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688856504741386</t>
+          <t>1688855071729227</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶一</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>如日方升</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10595,17 +10565,17 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高一</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>宋晓强</t>
+          <t>路跃威</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>songxiaoqiang</t>
+          <t>luyuewei</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -10650,37 +10620,37 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688857749872491</t>
+          <t>1688855073726560</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>劲揽山河-刘劲松</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -10694,17 +10664,17 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>王如梦</t>
+          <t>王泽</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>wangrumeng</t>
+          <t>wangze02</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -10749,32 +10719,32 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688854700793351</t>
+          <t>1688856187931330</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>云销雨霁-姚明</t>
+          <t>蒸蒸日上-曜-刘帅</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10789,21 +10759,26 @@
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>12,13</t>
+        </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>黄思旭</t>
+          <t>孙建通</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>huangsixu</t>
+          <t>sunjiantong01</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -10848,37 +10823,37 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688854847586533</t>
+          <t>1688858356858343</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -10892,17 +10867,17 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>李肖雨</t>
+          <t>黄梦雅</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>lixiaoyu</t>
+          <t>huangmengya</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -10947,32 +10922,32 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688856168895775</t>
+          <t>1688857014907414</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>经略四方-何佳泽</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10991,17 +10966,17 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>赵佳鑫</t>
+          <t>焦泽晖</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>zhaojiaxin01</t>
+          <t>jiaozehui01</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -11046,7 +11021,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688857525693645</t>
+          <t>1688857250838140</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -11056,27 +11031,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>功不唐捐-蒲世奥</t>
+          <t>劲揽山河-刘劲松</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0元</t>
+          <t>低价课</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -11095,12 +11070,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>何玉涵</t>
+          <t>张立</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>heyuhan</t>
+          <t>zhangli02</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -11145,32 +11120,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688858311666546</t>
+          <t>1688855925819373</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>高阶一</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>继往开来-姜志强</t>
+          <t>决胜千里-张韶开</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -11189,17 +11164,17 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>高一</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>王嘉磊</t>
+          <t>李伟业</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>wangjialei</t>
+          <t>liweiye02</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -11244,32 +11219,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688856854514012</t>
+          <t>1688857749872444</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>高阶二</t>
+          <t>高阶三</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>骁腾问鼎-王立进</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -11278,42 +11253,27 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>高二</t>
+          <t>高三</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>冯常增</t>
+          <t>王泳淇</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>fengchangzeng</t>
+          <t>wangyongqi01</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -11358,7 +11318,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688857859856215</t>
+          <t>1688856187931267</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -11368,22 +11328,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>蒸蒸日上-曜-刘帅</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -11407,12 +11367,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>邢爱斌</t>
+          <t>周士杰</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>xingaibin01</t>
+          <t>zhoushijie01</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -11457,7 +11417,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688857484684695</t>
+          <t>1688856504741386</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -11467,27 +11427,27 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>破浪前行-陈嘉博</t>
+          <t>功不唐捐-蒲世奥</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>低价课</t>
+          <t>0元</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -11506,12 +11466,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>解博帆</t>
+          <t>宋晓强</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>xiebofan</t>
+          <t>songxiaoqiang</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -11556,74 +11516,693 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688857472723498</t>
+          <t>1688858188639828</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>云销雨霁-姚明</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>王泽壮</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>wangzezhuang</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>王泽壮</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>wangzezhuang</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1688858067856980</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>高阶二</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>紫翼飞腾-商紫强</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>董常依娃</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>dongchangyiwa</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>董常依娃</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>dongchangyiwa</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1688857258634877</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>高阶三</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>经略四方-何佳泽</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>张晓芊</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>zhangxiaoqian01</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>张晓芊</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>zhangxiaoqian01</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1688858356858333</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>高阶三</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>骁腾问鼎-王立进</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>叶旭佳</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>yexujia</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>高三</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>叶旭佳</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>yexujia</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1688854777850591</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>蒸蒸日上-曜-刘帅</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>张宝芮</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>zhangbaorui</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>蒸蒸日上-兴-白铁</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>杨洪懿</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>yanghongyi01</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="M107" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
-      </c>
-      <c r="S107" t="inlineStr">
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
         <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
-        <is>
-          <t>张宝芮</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>zhangbaorui</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>杨洪懿</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>yanghongyi01</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
         <is>
           <t>高中</t>
         </is>
       </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>石家庄高短</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1688856804923400</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>高阶一</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>云销雨霁-姚明</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>万士兴</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>wanshixing</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="O112" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>高一</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>万士兴</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>wanshixing</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>20261023</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>高阶</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1688854346786588</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>高阶二</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>破浪前行-陈嘉博</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>张天笑</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>zhangtianxiao</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>1</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>高二</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>张天笑</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>zhangtianxiao</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>高中</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>石家庄高短</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
         <is>
           <t>石家庄高短</t>
         </is>
@@ -11698,7 +12277,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -11711,10 +12290,10 @@
         <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -11737,16 +12316,16 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="4">
@@ -11764,16 +12343,16 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="5">
@@ -11796,16 +12375,16 @@
         <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="6">
@@ -11828,16 +12407,16 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -11866,10 +12445,10 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -11893,10 +12472,10 @@
         <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -11916,19 +12495,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -11948,10 +12527,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -11960,7 +12539,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="11">
@@ -11980,16 +12559,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
@@ -12007,19 +12586,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="13">
@@ -12103,19 +12682,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
-        <v>0.625</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.625</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="16">
@@ -12144,10 +12723,10 @@
         <v>0.75</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -12162,19 +12741,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="18">
@@ -12189,19 +12768,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.84375</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7472527472527473</v>
+        <v>0.8125</v>
       </c>
     </row>
   </sheetData>
@@ -12231,7 +12810,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄高短）-10月19日</t>
+          <t>企微风灵全天在线情况通晒（石家庄高短）-10月21日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -12315,7 +12894,7 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
+          <t>蒸蒸日上-兴-白铁</t>
         </is>
       </c>
       <c r="D4" s="20" t="n">
@@ -12328,10 +12907,10 @@
         <v>0.8</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" s="21" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -12346,16 +12925,16 @@
         <v>9</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="6">
@@ -12370,16 +12949,16 @@
         <v>19</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.7368421052631579</v>
       </c>
     </row>
     <row r="7">
@@ -12398,16 +12977,16 @@
         <v>13</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="8">
@@ -12422,16 +13001,16 @@
         <v>8</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G8" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -12452,10 +13031,10 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -12476,10 +13055,10 @@
         <v>0.8</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -12495,19 +13074,19 @@
         </is>
       </c>
       <c r="D11" s="20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -12519,10 +13098,10 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>1</v>
@@ -12531,7 +13110,7 @@
         <v>5</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="13">
@@ -12543,16 +13122,16 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>1</v>
@@ -12567,19 +13146,19 @@
       </c>
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15">
@@ -12643,19 +13222,19 @@
         </is>
       </c>
       <c r="D17" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.625</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G17" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>0.625</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="18">
@@ -12676,10 +13255,10 @@
         <v>0.75</v>
       </c>
       <c r="G18" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -12691,19 +13270,19 @@
       </c>
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="20">
@@ -12719,19 +13298,19 @@
       </c>
       <c r="C20" s="12" t="inlineStr"/>
       <c r="D20" s="24" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.84375</v>
       </c>
       <c r="G20" s="23" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.7472527472527473</v>
+        <v>0.8125</v>
       </c>
     </row>
   </sheetData>
